--- a/data/trans_camb/P57_AF_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,99; -3,38</t>
+          <t>-19,49; -3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,92; -3,07</t>
+          <t>-18,42; -3,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,14; -23,53</t>
+          <t>-39,83; -23,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -2,47</t>
+          <t>-16,45; -2,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,5; -7,05</t>
+          <t>-20,47; -6,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,74; -26,07</t>
+          <t>-39,83; -26,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -5,48</t>
+          <t>-15,31; -5,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,52; -7,23</t>
+          <t>-17,71; -7,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-37,68; -26,39</t>
+          <t>-37,67; -26,81</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,86; -4,68</t>
+          <t>-24,3; -4,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,68; -4,33</t>
+          <t>-22,94; -4,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,67; -31,52</t>
+          <t>-50,32; -31,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,97; -2,98</t>
+          <t>-18,69; -3,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,37; -8,48</t>
+          <t>-22,89; -7,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,01; -31,36</t>
+          <t>-45,18; -32,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,59; -6,75</t>
+          <t>-18,37; -7,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,13; -9,15</t>
+          <t>-21,22; -9,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,32; -33,16</t>
+          <t>-45,61; -33,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -2,37</t>
+          <t>-15,42; -2,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,92; 26,9</t>
+          <t>15,35; 27,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 2,81</t>
+          <t>-11,54; 3,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,46; -4,87</t>
+          <t>-17,81; -5,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,62; 23,55</t>
+          <t>12,57; 23,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -4,3</t>
+          <t>-15,98; -3,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,99; -5,72</t>
+          <t>-15,01; -5,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,38; 23,49</t>
+          <t>15,48; 23,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -3,03</t>
+          <t>-11,93; -2,8</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,63; -4,26</t>
+          <t>-24,69; -4,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,61; 48,52</t>
+          <t>24,07; 48,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 4,95</t>
+          <t>-18,43; 6,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,58; -8,05</t>
+          <t>-27,25; -9,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,02; 39,3</t>
+          <t>18,87; 39,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,69; -7,16</t>
+          <t>-24,2; -6,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,51; -9,69</t>
+          <t>-23,85; -9,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,22; 40,13</t>
+          <t>24,39; 40,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-18,91; -5,07</t>
+          <t>-18,73; -4,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 19,07</t>
+          <t>3,89; 20,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,63; 32,72</t>
+          <t>17,32; 32,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 2,38</t>
+          <t>-15,18; 1,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,97; 33,59</t>
+          <t>17,85; 32,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,35; 41,64</t>
+          <t>28,73; 42,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 13,52</t>
+          <t>-0,61; 14,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,23; 24,38</t>
+          <t>13,78; 24,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,16; 35,48</t>
+          <t>25,02; 35,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 5,31</t>
+          <t>-5,08; 5,07</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,65; 44,79</t>
+          <t>7,72; 48,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36,14; 77,95</t>
+          <t>34,73; 79,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 5,79</t>
+          <t>-30,06; 2,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39,27; 92,02</t>
+          <t>40,95; 87,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,61; 113,01</t>
+          <t>63,72; 116,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 36,84</t>
+          <t>-1,28; 37,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,43; 58,92</t>
+          <t>29,76; 59,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,42; 87,0</t>
+          <t>53,35; 87,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 12,65</t>
+          <t>-10,83; 12,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,96; -10,5</t>
+          <t>-24,53; -9,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -20,75</t>
+          <t>-35,61; -21,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-46,18; -31,32</t>
+          <t>-45,87; -31,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 0,74</t>
+          <t>-12,93; 0,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,06; -15,24</t>
+          <t>-29,22; -15,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,36; -30,01</t>
+          <t>-48,24; -30,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,04; -6,73</t>
+          <t>-16,69; -6,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,56; -20,19</t>
+          <t>-30,48; -20,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-45,95; -33,21</t>
+          <t>-45,53; -33,6</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,67; -17,68</t>
+          <t>-37,08; -16,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,39; -33,78</t>
+          <t>-53,03; -35,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,26; -51,59</t>
+          <t>-69,38; -51,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 1,54</t>
+          <t>-20,21; 0,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,01; -26,02</t>
+          <t>-45,14; -26,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,24; -50,93</t>
+          <t>-76,9; -50,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,09; -11,13</t>
+          <t>-25,69; -10,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,38; -33,39</t>
+          <t>-46,95; -33,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,32; -54,25</t>
+          <t>-71,12; -54,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,33; -5,96</t>
+          <t>-24,41; -6,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,62; 24,82</t>
+          <t>8,38; 24,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,29; 31,12</t>
+          <t>15,07; 30,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 1,43</t>
+          <t>-15,55; 1,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,89; 19,33</t>
+          <t>3,99; 20,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,0; 23,38</t>
+          <t>9,96; 23,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,38; -4,58</t>
+          <t>-18,31; -4,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,58; 19,67</t>
+          <t>8,0; 19,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,97; 24,93</t>
+          <t>14,89; 25,5</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,75; -8,82</t>
+          <t>-33,96; -10,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11,85; 39,43</t>
+          <t>11,49; 38,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,69; 50,17</t>
+          <t>20,49; 49,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 1,97</t>
+          <t>-19,93; 1,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,91; 28,32</t>
+          <t>5,16; 29,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,78; 34,01</t>
+          <t>12,87; 34,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,48; -6,67</t>
+          <t>-24,67; -7,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11,57; 29,5</t>
+          <t>10,71; 28,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19,79; 37,17</t>
+          <t>19,55; 38,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 8,29</t>
+          <t>-8,3; 8,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,56; 21,58</t>
+          <t>4,86; 21,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-30,54; -15,24</t>
+          <t>-30,63; -14,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,8; 20,78</t>
+          <t>4,02; 19,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,61; 28,95</t>
+          <t>13,85; 29,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-25,97; -10,79</t>
+          <t>-25,63; -11,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 12,23</t>
+          <t>0,36; 12,26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>12,02; 23,15</t>
+          <t>12,26; 23,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-25,92; -15,33</t>
+          <t>-25,7; -14,61</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 15,28</t>
+          <t>-13,24; 16,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8,71; 39,85</t>
+          <t>7,87; 40,11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,08; -27,73</t>
+          <t>-48,93; -27,48</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,61; 40,84</t>
+          <t>6,67; 40,09</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22,29; 56,57</t>
+          <t>22,61; 58,37</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-43,65; -21,63</t>
+          <t>-43,13; -21,39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,07; 22,71</t>
+          <t>0,61; 22,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>19,9; 43,42</t>
+          <t>19,97; 44,4</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,31; -28,33</t>
+          <t>-43,36; -28,12</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,7; 18,42</t>
+          <t>6,35; 17,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30,57; 41,07</t>
+          <t>30,57; 41,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,97; 18,25</t>
+          <t>5,81; 18,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19,27; 30,09</t>
+          <t>19,86; 30,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>35,51; 45,64</t>
+          <t>35,58; 45,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,12; 47,35</t>
+          <t>14,43; 46,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,84; 22,86</t>
+          <t>15,19; 22,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>34,67; 41,84</t>
+          <t>34,39; 42,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,67; 35,95</t>
+          <t>13,2; 38,09</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,86; 47,17</t>
+          <t>13,47; 44,01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>66,36; 103,34</t>
+          <t>65,44; 103,07</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,4; 45,36</t>
+          <t>12,65; 45,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49,08; 92,14</t>
+          <t>50,39; 92,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>89,75; 139,7</t>
+          <t>91,13; 140,92</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,79; 141,78</t>
+          <t>39,59; 136,66</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,1; 61,86</t>
+          <t>36,73; 61,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>83,03; 112,99</t>
+          <t>82,78; 114,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>31,34; 94,66</t>
+          <t>33,2; 101,33</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>8,63; 17,21</t>
+          <t>8,9; 16,93</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7,23; 15,91</t>
+          <t>7,81; 15,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 9,53</t>
+          <t>-46,23; 9,63</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,06; 7,79</t>
+          <t>-0,45; 7,35</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,71; 12,19</t>
+          <t>4,5; 12,09</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,59</t>
+          <t>1,2; 8,6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,12</t>
+          <t>5,22; 11,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,37; 12,79</t>
+          <t>7,07; 12,95</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 7,31</t>
+          <t>-36,98; 7,4</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>11,52; 24,32</t>
+          <t>11,79; 24,16</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9,65; 22,84</t>
+          <t>10,41; 22,56</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 13,07</t>
+          <t>-62,37; 13,43</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0,12; 10,07</t>
+          <t>-0,44; 9,63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,86; 15,79</t>
+          <t>5,44; 15,68</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,04; 11,07</t>
+          <t>1,52; 11,17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,06; 14,83</t>
+          <t>6,84; 15,15</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,45; 17,14</t>
+          <t>9,02; 17,45</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 9,68</t>
+          <t>-48,45; 9,8</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,62</t>
+          <t>-1,37; 3,76</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>10,82; 15,61</t>
+          <t>10,97; 15,62</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-20,79; -3,97</t>
+          <t>-20,43; -3,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,91</t>
+          <t>3,11; 7,76</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,11</t>
+          <t>12,67; 17,21</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,29</t>
+          <t>-7,13; 4,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,12</t>
+          <t>1,76; 5,19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>12,5; 15,69</t>
+          <t>12,47; 15,73</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -1,96</t>
+          <t>-12,31; -1,77</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,13</t>
+          <t>-2,23; 6,36</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>17,41; 26,34</t>
+          <t>17,65; 26,52</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -6,52</t>
+          <t>-32,62; -6,3</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,22</t>
+          <t>4,96; 13,03</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>20,23; 28,42</t>
+          <t>20,3; 28,95</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 7,1</t>
+          <t>-11,44; 8,22</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,48</t>
+          <t>2,82; 8,61</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>20,15; 26,15</t>
+          <t>20,29; 26,39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-19,03; -3,2</t>
+          <t>-19,9; -2,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AF_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-31,73</t>
+          <t>-28,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-33,27</t>
+          <t>-32,42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-32,52</t>
+          <t>-30,14</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,49; -3,58</t>
+          <t>-18,96; -4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,42; -3,25</t>
+          <t>-17,93; -3,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,83; -23,29</t>
+          <t>-35,39; -20,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,45; -2,65</t>
+          <t>-16,39; -1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -6,28</t>
+          <t>-20,73; -6,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,83; -26,6</t>
+          <t>-38,6; -26,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -5,62</t>
+          <t>-16,09; -5,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -7,45</t>
+          <t>-17,59; -7,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-37,67; -26,81</t>
+          <t>-34,92; -24,52</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-40,95%</t>
+          <t>-36,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-38,69%</t>
+          <t>-37,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-39,84%</t>
+          <t>-36,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,3; -4,81</t>
+          <t>-23,62; -5,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,94; -4,42</t>
+          <t>-22,72; -4,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,32; -31,19</t>
+          <t>-44,55; -27,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,69; -3,22</t>
+          <t>-18,82; -2,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -7,45</t>
+          <t>-23,21; -8,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,18; -32,29</t>
+          <t>-43,71; -31,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -7,0</t>
+          <t>-19,08; -7,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,22; -9,34</t>
+          <t>-20,79; -9,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,61; -33,63</t>
+          <t>-41,84; -31,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,18</t>
+          <t>-3,59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-10,39</t>
+          <t>-10,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-7,3</t>
+          <t>-7,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,42; -2,37</t>
+          <t>-15,93; -2,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,35; 27,11</t>
+          <t>15,27; 27,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 3,57</t>
+          <t>-11,19; 3,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,81; -5,31</t>
+          <t>-17,48; -5,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 23,62</t>
+          <t>13,07; 23,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -3,78</t>
+          <t>-16,82; -4,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,01; -5,61</t>
+          <t>-15,05; -6,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,48; 23,62</t>
+          <t>15,5; 23,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -2,8</t>
+          <t>-11,6; -2,35</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,01%</t>
+          <t>-6,02%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,43%</t>
+          <t>-16,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-11,88%</t>
+          <t>-11,48%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,69; -4,43</t>
+          <t>-25,51; -4,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,07; 48,67</t>
+          <t>24,29; 49,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 6,64</t>
+          <t>-17,75; 5,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,25; -9,09</t>
+          <t>-26,86; -8,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,87; 39,57</t>
+          <t>19,73; 39,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,2; -6,27</t>
+          <t>-25,12; -7,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,85; -9,74</t>
+          <t>-23,91; -10,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,39; 40,27</t>
+          <t>24,06; 40,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-18,73; -4,84</t>
+          <t>-18,05; -3,92</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,84</t>
+          <t>-6,21</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>6,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 20,38</t>
+          <t>4,47; 20,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,32; 32,73</t>
+          <t>18,16; 33,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 1,23</t>
+          <t>-14,01; 1,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 32,23</t>
+          <t>18,43; 32,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,73; 42,44</t>
+          <t>28,33; 41,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 14,0</t>
+          <t>0,26; 13,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,78; 24,14</t>
+          <t>13,88; 24,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,02; 35,53</t>
+          <t>25,63; 35,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 5,07</t>
+          <t>-4,18; 5,69</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-14,66%</t>
+          <t>-13,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-0,11%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,72; 48,73</t>
+          <t>8,43; 50,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,73; 79,32</t>
+          <t>35,67; 79,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 2,93</t>
+          <t>-27,33; 4,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40,95; 87,85</t>
+          <t>40,9; 86,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63,72; 116,54</t>
+          <t>61,65; 114,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 37,64</t>
+          <t>0,55; 36,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,76; 59,34</t>
+          <t>29,79; 59,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,35; 87,66</t>
+          <t>54,62; 87,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 12,43</t>
+          <t>-8,98; 13,41</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-39,16</t>
+          <t>-38,75</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-37,9</t>
+          <t>-31,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-38,64</t>
+          <t>-34,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,53; -9,44</t>
+          <t>-25,03; -9,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-35,61; -21,27</t>
+          <t>-36,49; -21,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-45,87; -31,28</t>
+          <t>-45,97; -31,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 0,46</t>
+          <t>-12,62; 1,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,22; -15,41</t>
+          <t>-28,95; -14,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,24; -30,08</t>
+          <t>-37,73; -24,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,69; -6,6</t>
+          <t>-16,66; -6,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,48; -20,29</t>
+          <t>-30,27; -19,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-45,53; -33,6</t>
+          <t>-39,48; -29,83</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-61,17%</t>
+          <t>-60,52%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-61,6%</t>
+          <t>-50,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-61,57%</t>
+          <t>-55,51%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,08; -16,09</t>
+          <t>-37,25; -15,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-53,03; -35,0</t>
+          <t>-53,25; -34,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -51,96</t>
+          <t>-69,36; -50,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 0,99</t>
+          <t>-19,96; 2,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,14; -26,11</t>
+          <t>-45,36; -25,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,9; -50,77</t>
+          <t>-58,06; -42,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,69; -10,7</t>
+          <t>-25,74; -10,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,95; -33,01</t>
+          <t>-46,61; -32,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,12; -54,65</t>
+          <t>-60,88; -49,09</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>22,55</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,92</t>
+          <t>17,38</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20,02</t>
+          <t>19,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,41; -6,15</t>
+          <t>-25,35; -5,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,38; 24,17</t>
+          <t>8,16; 24,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15,07; 30,68</t>
+          <t>14,42; 30,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 1,25</t>
+          <t>-15,89; 1,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,99; 20,29</t>
+          <t>3,6; 19,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,96; 23,85</t>
+          <t>11,17; 24,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -4,95</t>
+          <t>-17,22; -4,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,0; 19,33</t>
+          <t>8,16; 19,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,89; 25,5</t>
+          <t>15,43; 25,82</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,96; -10,22</t>
+          <t>-35,35; -9,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11,49; 38,85</t>
+          <t>10,97; 39,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,49; 49,5</t>
+          <t>19,66; 48,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 1,6</t>
+          <t>-20,52; 2,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,16; 29,42</t>
+          <t>4,38; 28,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,87; 34,93</t>
+          <t>14,21; 36,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -7,3</t>
+          <t>-23,67; -6,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10,71; 28,69</t>
+          <t>11,14; 29,33</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19,55; 38,19</t>
+          <t>20,21; 38,4</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-22,99</t>
+          <t>-21,32</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-18,63</t>
+          <t>-17,41</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-20,8</t>
+          <t>-19,34</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 8,63</t>
+          <t>-9,34; 7,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,86; 21,92</t>
+          <t>5,3; 21,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -14,86</t>
+          <t>-29,31; -14,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,02; 19,89</t>
+          <t>3,29; 19,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,85; 29,32</t>
+          <t>14,3; 29,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-25,63; -11,37</t>
+          <t>-24,79; -10,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,36; 12,26</t>
+          <t>0,06; 11,97</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>12,26; 23,66</t>
+          <t>11,85; 23,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-25,7; -14,61</t>
+          <t>-24,45; -13,49</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-39,03%</t>
+          <t>-36,18%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-33,66%</t>
+          <t>-31,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-36,42%</t>
+          <t>-33,87%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 16,45</t>
+          <t>-14,99; 13,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7,87; 40,11</t>
+          <t>8,57; 39,06</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,93; -27,48</t>
+          <t>-46,2; -25,26</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,67; 40,09</t>
+          <t>5,34; 38,16</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22,61; 58,37</t>
+          <t>24,27; 58,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-43,13; -21,39</t>
+          <t>-41,65; -20,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,61; 22,93</t>
+          <t>0,11; 22,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>19,97; 44,4</t>
+          <t>19,92; 43,86</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,36; -28,12</t>
+          <t>-41,1; -25,53</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,3</t>
+          <t>12,04</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,85</t>
+          <t>16,92</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>20,76</t>
+          <t>14,51</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,35; 17,61</t>
+          <t>6,26; 17,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30,57; 41,13</t>
+          <t>30,28; 40,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,81; 18,4</t>
+          <t>5,81; 17,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19,86; 30,47</t>
+          <t>19,43; 30,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>35,58; 45,83</t>
+          <t>35,36; 45,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,43; 46,5</t>
+          <t>11,5; 21,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,19; 22,69</t>
+          <t>15,43; 22,97</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>34,39; 42,21</t>
+          <t>34,88; 42,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,2; 38,09</t>
+          <t>10,89; 18,38</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,47; 44,01</t>
+          <t>13,5; 45,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>65,44; 103,07</t>
+          <t>65,17; 103,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12,65; 45,7</t>
+          <t>12,5; 43,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50,39; 92,87</t>
+          <t>49,3; 91,46</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>91,13; 140,92</t>
+          <t>89,87; 139,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,59; 136,66</t>
+          <t>29,07; 64,91</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,73; 61,53</t>
+          <t>37,2; 62,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>82,78; 114,06</t>
+          <t>84,04; 114,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,2; 101,33</t>
+          <t>26,41; 49,33</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-13,2</t>
+          <t>8,41</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,86</t>
+          <t>6,4</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>8,9; 16,93</t>
+          <t>8,92; 16,98</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7,81; 15,85</t>
+          <t>7,78; 16,18</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 9,63</t>
+          <t>4,15; 12,91</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 7,35</t>
+          <t>-0,0; 7,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,09</t>
+          <t>4,81; 12,29</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,6</t>
+          <t>0,34; 8,32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,22; 11,19</t>
+          <t>5,39; 10,86</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,07; 12,95</t>
+          <t>7,12; 12,64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 7,4</t>
+          <t>3,49; 9,46</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-18,12%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-7,68%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>11,79; 24,16</t>
+          <t>11,49; 23,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,41; 22,56</t>
+          <t>10,16; 22,92</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 13,43</t>
+          <t>5,47; 18,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 9,63</t>
+          <t>0,03; 10,01</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,44; 15,68</t>
+          <t>6,03; 16,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,52; 11,17</t>
+          <t>0,39; 10,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,84; 15,15</t>
+          <t>6,95; 14,38</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,02; 17,45</t>
+          <t>9,13; 16,98</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 9,8</t>
+          <t>4,47; 12,65</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-8,8</t>
+          <t>-3,7</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-3,06</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-5,78</t>
+          <t>-3,37</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,76</t>
+          <t>-1,0; 3,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>10,97; 15,62</t>
+          <t>10,95; 15,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -3,79</t>
+          <t>-6,47; -1,2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,76</t>
+          <t>3,27; 7,91</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,21</t>
+          <t>12,68; 17,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 4,94</t>
+          <t>-5,31; -0,77</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,19</t>
+          <t>1,79; 5,08</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>12,47; 15,73</t>
+          <t>12,37; 15,65</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -1,77</t>
+          <t>-5,18; -1,71</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-14,51%</t>
+          <t>-6,09%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-4,77%</t>
+          <t>-4,99%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-9,48%</t>
+          <t>-5,52%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 6,36</t>
+          <t>-1,66; 5,88</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>17,65; 26,52</t>
+          <t>17,75; 26,05</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-32,62; -6,3</t>
+          <t>-10,53; -1,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,03</t>
+          <t>5,19; 13,07</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>20,3; 28,95</t>
+          <t>20,29; 28,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 8,22</t>
+          <t>-8,45; -1,28</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,61</t>
+          <t>2,91; 8,43</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>20,29; 26,39</t>
+          <t>19,85; 26,0</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-19,9; -2,9</t>
+          <t>-8,4; -2,82</t>
         </is>
       </c>
     </row>
